--- a/Cumulative_Outputs/Results/Results_T-All_K1.N10.P0.xlsx
+++ b/Cumulative_Outputs/Results/Results_T-All_K1.N10.P0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Boolean_Network_SISOR_Degeneracy_Simulator\Boolean_Network_SISOR_Degeneracy_Simulator\Cumulative_Outputs\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C5AF7E-0ECB-4F9A-88C9-C0B860F6E46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DC015F-D092-4DDD-90E3-8320C18FE2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="26580" windowHeight="15840" activeTab="3" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
   </bookViews>
   <sheets>
     <sheet name="T-All_K1 N10 P0" sheetId="7" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="46">
   <si>
     <t>Identifier</t>
   </si>
@@ -187,6 +187,12 @@
   <si>
     <t>s</t>
   </si>
+  <si>
+    <t>Average per ID</t>
+  </si>
+  <si>
+    <t>Average per Timestep</t>
+  </si>
 </sst>
 </file>
 
@@ -285,18 +291,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +493,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-AU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5758,7 +5763,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -8816,7 +8820,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="B2">
@@ -8848,7 +8852,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
       <c r="B3">
@@ -8880,7 +8884,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4">
@@ -8912,7 +8916,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5">
@@ -8944,7 +8948,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
       <c r="B6">
@@ -8976,7 +8980,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" t="s">
         <v>27</v>
       </c>
       <c r="B7">
@@ -9008,7 +9012,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8">
@@ -9040,7 +9044,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" t="s">
         <v>29</v>
       </c>
       <c r="B9">
@@ -9072,7 +9076,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
       <c r="B10">
@@ -9104,7 +9108,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
       <c r="B11">
@@ -9136,7 +9140,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
       <c r="B12">
@@ -9168,7 +9172,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" t="s">
         <v>42</v>
       </c>
       <c r="B13">
@@ -9955,7 +9959,7 @@
         <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>21</v>
@@ -10562,7 +10566,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B20" s="7">
         <f>AVERAGE(B2:B13)</f>
@@ -10615,7 +10619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576">
+  <conditionalFormatting sqref="K1:L24 K26:L1048576 K25">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -10681,7 +10685,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
@@ -10713,7 +10717,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
@@ -10745,7 +10749,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
@@ -10777,7 +10781,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
@@ -10809,7 +10813,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7">
@@ -10841,7 +10845,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8">
@@ -10873,7 +10877,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9">
@@ -10905,7 +10909,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
       <c r="B10">
@@ -10937,7 +10941,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
       <c r="B11">
@@ -10969,7 +10973,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" t="s">
         <v>34</v>
       </c>
       <c r="B12">
@@ -11001,7 +11005,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13">
@@ -11033,7 +11037,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
       <c r="B14">

--- a/Cumulative_Outputs/Results/Results_T-All_K1.N10.P0.xlsx
+++ b/Cumulative_Outputs/Results/Results_T-All_K1.N10.P0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Boolean_Network_SISOR_Degeneracy_Simulator\Boolean_Network_SISOR_Degeneracy_Simulator\Cumulative_Outputs\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DC015F-D092-4DDD-90E3-8320C18FE2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394E6A13-67FC-4637-8D7C-634EC41A8648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="26580" windowHeight="15840" activeTab="3" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{8979E4B9-F6D3-4FFF-BFAD-32F04701C466}"/>
   </bookViews>
   <sheets>
     <sheet name="T-All_K1 N10 P0" sheetId="7" r:id="rId1"/>
@@ -10619,7 +10619,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L24 K26:L1048576 K25">
+  <conditionalFormatting sqref="K1:L24 K25 K26:L1048576">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
